--- a/data/output/evaluasi_94.xlsx
+++ b/data/output/evaluasi_94.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet name="9400" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="9419" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="9471" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="9420" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="9426" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="9427" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="9409" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="9428" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9420" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9471" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9409" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9426" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="9408" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="9427" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9428" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,16 +483,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-8.955028837572081</v>
+        <v>7.769458137214963</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -510,16 +511,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-8.028651061821442</v>
+        <v>8.067264072235734</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -534,20 +535,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.175680227358241</v>
+        <v>12.23045615361632</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -562,20 +563,384 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.81958696550825</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.46690076518561</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.545738004867781</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.100520812863992</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.889128484663953</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>-0.1725624700413581</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pdrb_q1-25 vs implisit_q-to-q_pdrb_q1-25.1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D10" t="n">
+        <v>-8.920156751054902</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5643140189454741</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.902479082795689</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.460531955158395</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>94</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-8.920156751054902</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.394378988250583</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.902479082795689</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.750602929868748</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>94</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Papua</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1225345360368367</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -590,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,16 +1005,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-20164.74289390818</v>
+        <v>-7.202887425443388</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -668,16 +1033,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-22804.47426262358</v>
+        <v>-5.963360192654339</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -692,20 +1057,76 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.007874228806877595</v>
+        <v>-4.311966298493923</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.10085562021104</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9419</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sarmi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.501321685961037</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -720,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,11 +1178,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9471</v>
+        <v>9420</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Jayapura</t>
+          <t>Kabupaten Keerom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -770,26 +1191,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82607.47508554276</v>
+        <v>3.972750383009711</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9471</v>
+        <v>9420</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Jayapura</t>
+          <t>Kabupaten Keerom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -798,16 +1219,128 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39124.82556647158</v>
+        <v>-2.662689670073192</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.223894366566415</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.4079680621515051</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.183192328389354</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9420</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Keerom</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.313095315969157</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -822,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,11 +1392,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9420</v>
+        <v>9471</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Keerom</t>
+          <t>Kota Jayapura</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -872,128 +1405,44 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.292417570435145</v>
+        <v>4.078020641504647</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9420</v>
+        <v>9471</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Keerom</t>
+          <t>Kota Jayapura</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.292417570435145</v>
+        <v>-2.016775082192996</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9420</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kabupaten Keerom</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1569507013156857</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>9420</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Keerom</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2412624951887093</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9420</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Keerom</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6274294314774748</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,85 +1494,309 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9426</v>
+        <v>9409</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Waropen</t>
+          <t>Kabupaten Biak Numfor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.130999630888987</v>
+        <v>-2.114177278410357</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9426</v>
+        <v>9409</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Waropen</t>
+          <t>Kabupaten Biak Numfor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.130999630888987</v>
+        <v>-0.3965442522449047</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9426</v>
+        <v>9409</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Waropen</t>
+          <t>Kabupaten Biak Numfor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4976070096371842</v>
+        <v>0.162111912989149</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.94722084898572</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5074427992291494</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.205342940583666</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4147663908284197</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.288818936111785</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.301980449799998</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3034249791136348</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Biak Numfor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.348510553361542</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,141 +1848,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9427</v>
+        <v>9426</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Supiori</t>
+          <t>Kabupaten Waropen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.194613774482941</v>
+        <v>1.266366416351409</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9427</v>
+        <v>9426</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Supiori</t>
+          <t>Kabupaten Waropen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.194613774482941</v>
+        <v>-2.18447674098679</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9427</v>
+        <v>9426</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Supiori</t>
+          <t>Kabupaten Waropen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1863625243234508</v>
+        <v>6.556271199829082</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9427</v>
+        <v>9426</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Supiori</t>
+          <t>Kabupaten Waropen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.309061984038377</v>
+        <v>3.824918181479932</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9427</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Supiori</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.3089519463304017</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1361,29 +2006,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9409</v>
+        <v>9408</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Biak Numfor</t>
+          <t>Kabupaten Kepulauan Yapen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.01357404844255114</v>
+        <v>-1.701193020505076</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.65717657872761</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5816595779801061</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.614578796415148</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.366726241082709</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1398,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1435,6 +2192,108 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.1322442118142</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9427</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Supiori</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.348981714194075</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9428</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1444,20 +2303,160 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05082393628638817</v>
+        <v>-5.817298456787663</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.53556096770612</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5058827226610177</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5509130194594622</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.490348057636237</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9428</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.549706657314646</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_94.xlsx
+++ b/data/output/evaluasi_94.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
